--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\TIM 2100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC284C4A-2A9D-4CEB-9206-1C51106AA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127B12DA-DD54-4E4D-B927-418F6DADE12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="171">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -641,7 +641,10 @@
     <t>Bakytzhan Suleimenov (UCC, bsuleimenov@ucc.ie)</t>
   </si>
   <si>
-    <t>P24</t>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>P54</t>
   </si>
 </sst>
 </file>
@@ -4012,18 +4015,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3D08AF-561B-4741-93FB-876D250B4223}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="21.6640625" style="42" customWidth="1"/>
-    <col min="5" max="6" width="14.109375" style="42" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="42" customWidth="1"/>
-    <col min="8" max="10" width="8.109375" style="42" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="42" customWidth="1"/>
-    <col min="12" max="12" width="8.109375" style="42" customWidth="1"/>
+    <col min="1" max="4" width="21.77734375" style="42" customWidth="1"/>
+    <col min="5" max="6" width="14.21875" style="42" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" style="42" customWidth="1"/>
+    <col min="8" max="10" width="8.21875" style="42" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" style="42" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" style="42" customWidth="1"/>
     <col min="13" max="13" width="10" style="42" customWidth="1"/>
     <col min="14" max="14" width="11.44140625" style="42" customWidth="1"/>
     <col min="15" max="15" width="13.44140625" style="42" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="42"/>
+    <col min="16" max="16384" width="8.77734375" style="42"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
@@ -6862,33 +6865,32 @@
   <dimension ref="A3:AD37"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="3.21875" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" customWidth="1"/>
     <col min="5" max="5" width="6.44140625" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="7" max="8" width="5.77734375" customWidth="1"/>
     <col min="9" max="9" width="5.44140625" customWidth="1"/>
-    <col min="10" max="11" width="5.6640625" customWidth="1"/>
+    <col min="10" max="11" width="5.77734375" customWidth="1"/>
     <col min="12" max="12" width="6.5546875" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" customWidth="1"/>
     <col min="15" max="15" width="6.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.109375" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.21875" customWidth="1"/>
+    <col min="17" max="17" width="5.77734375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" customWidth="1"/>
     <col min="20" max="20" width="5.5546875" customWidth="1"/>
-    <col min="21" max="21" width="5.88671875" customWidth="1"/>
-    <col min="22" max="22" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" customWidth="1"/>
     <col min="23" max="23" width="5" customWidth="1"/>
     <col min="24" max="24" width="7.5546875" customWidth="1"/>
-    <col min="25" max="25" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="6.77734375" customWidth="1"/>
     <col min="26" max="28" width="6" customWidth="1"/>
-    <col min="29" max="29" width="5.6640625" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="5.77734375" customWidth="1"/>
+    <col min="30" max="30" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7540,7 +7542,7 @@
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" customWidth="1"/>
     <col min="5" max="5" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7803,41 +7805,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B3:V51"/>
+  <dimension ref="B3:Y66"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="9" width="13.6640625" customWidth="1"/>
+    <col min="2" max="9" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="11"/>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>137</v>
       </c>
@@ -7868,38 +7870,44 @@
       <c r="K12" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="L12" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="O12" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="P12" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="Q12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="39" t="s">
+      <c r="R12" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="Q12" s="13" t="s">
+      <c r="S12" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R12" s="39" t="s">
+      <c r="T12" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="S12" s="39" t="s">
+      <c r="U12" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="T12" s="39" t="s">
+      <c r="V12" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="W12" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="X12" s="13" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="Y12" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>1</v>
       </c>
@@ -7930,48 +7938,55 @@
       <c r="K13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="12">
+      <c r="L13" s="17">
+        <v>1</v>
+      </c>
+      <c r="O13" s="12">
         <f>+B4</f>
         <v>2018</v>
       </c>
-      <c r="N13" s="12">
-        <f>+M13</f>
+      <c r="P13" s="12">
+        <f>+O13</f>
         <v>2018</v>
       </c>
-      <c r="O13" s="12">
-        <f t="shared" ref="O13:T13" si="0">+N13</f>
-        <v>2018</v>
-      </c>
-      <c r="P13" s="12">
-        <f t="shared" si="0"/>
-        <v>2018</v>
-      </c>
       <c r="Q13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Q13:V13" si="0">+P13</f>
         <v>2018</v>
       </c>
       <c r="R13" s="12">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="S13" s="17">
+      <c r="S13" s="12">
+        <f>+R13</f>
+        <v>2018</v>
+      </c>
+      <c r="T13" s="12">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="T13" s="17">
+      <c r="U13" s="17">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="U13" s="17">
-        <f t="shared" ref="U13:V13" si="1">+T13</f>
+      <c r="V13" s="17">
+        <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="V13" s="17">
+      <c r="W13" s="17">
+        <f t="shared" ref="W13:Y13" si="1">+V13</f>
+        <v>2018</v>
+      </c>
+      <c r="X13" s="17">
         <f t="shared" si="1"/>
         <v>2018</v>
       </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="Y13" s="17">
+        <f t="shared" si="1"/>
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>1</v>
       </c>
@@ -8002,35 +8017,30 @@
       <c r="K14" s="12">
         <v>1</v>
       </c>
-      <c r="M14" s="12">
-        <f>+M13+B14</f>
+      <c r="L14" s="17">
+        <v>1</v>
+      </c>
+      <c r="O14" s="12">
+        <f t="shared" ref="O14:W17" si="2">+O13+B14</f>
         <v>2019</v>
       </c>
-      <c r="N14" s="12">
-        <f t="shared" ref="N14:V29" si="2">+N13+C14</f>
+      <c r="P14" s="12">
+        <f t="shared" si="2"/>
         <v>2019</v>
       </c>
-      <c r="O14" s="12">
+      <c r="Q14" s="12">
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-      <c r="P14" s="12">
+      <c r="R14" s="12">
         <f t="shared" si="2"/>
         <v>2021</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="S14" s="12">
         <f t="shared" si="2"/>
         <v>2019</v>
       </c>
-      <c r="R14" s="12">
-        <f t="shared" si="2"/>
-        <v>2019</v>
-      </c>
-      <c r="S14" s="17">
-        <f t="shared" si="2"/>
-        <v>2019</v>
-      </c>
-      <c r="T14" s="17">
+      <c r="T14" s="12">
         <f t="shared" si="2"/>
         <v>2019</v>
       </c>
@@ -8042,8 +8052,20 @@
         <f t="shared" si="2"/>
         <v>2019</v>
       </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W14" s="17">
+        <f t="shared" si="2"/>
+        <v>2019</v>
+      </c>
+      <c r="X14" s="17">
+        <f>X13+K14</f>
+        <v>2019</v>
+      </c>
+      <c r="Y14" s="17">
+        <f>Y13+L14</f>
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>1</v>
       </c>
@@ -8074,35 +8096,30 @@
       <c r="K15" s="12">
         <v>1</v>
       </c>
-      <c r="M15" s="12">
-        <f t="shared" ref="M15:M17" si="3">+M14+B15</f>
-        <v>2020</v>
-      </c>
-      <c r="N15" s="12">
+      <c r="L15" s="17">
+        <v>1</v>
+      </c>
+      <c r="O15" s="12">
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
-      <c r="O15" s="12">
+      <c r="P15" s="12">
+        <f t="shared" si="2"/>
+        <v>2020</v>
+      </c>
+      <c r="Q15" s="12">
         <f t="shared" si="2"/>
         <v>2027</v>
       </c>
-      <c r="P15" s="12">
+      <c r="R15" s="12">
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="S15" s="12">
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
-      <c r="R15" s="12">
-        <f t="shared" si="2"/>
-        <v>2020</v>
-      </c>
-      <c r="S15" s="17">
-        <f t="shared" si="2"/>
-        <v>2020</v>
-      </c>
-      <c r="T15" s="17">
+      <c r="T15" s="12">
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
@@ -8114,8 +8131,20 @@
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W15" s="17">
+        <f t="shared" si="2"/>
+        <v>2020</v>
+      </c>
+      <c r="X15" s="17">
+        <f>X14+K15</f>
+        <v>2020</v>
+      </c>
+      <c r="Y15" s="17">
+        <f>Y14+L15</f>
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
         <v>20</v>
       </c>
@@ -8146,35 +8175,30 @@
       <c r="K16" s="12">
         <v>1</v>
       </c>
-      <c r="M16" s="12">
-        <f t="shared" si="3"/>
+      <c r="L16" s="17">
+        <v>1</v>
+      </c>
+      <c r="O16" s="12">
+        <f t="shared" si="2"/>
         <v>2040</v>
       </c>
-      <c r="N16" s="12">
+      <c r="P16" s="12">
         <f t="shared" si="2"/>
         <v>2021</v>
       </c>
-      <c r="O16" s="12">
+      <c r="Q16" s="12">
         <f t="shared" si="2"/>
         <v>2032</v>
       </c>
-      <c r="P16" s="12">
+      <c r="R16" s="12">
         <f t="shared" si="2"/>
         <v>2027</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="S16" s="12">
         <f t="shared" si="2"/>
         <v>2021</v>
       </c>
-      <c r="R16" s="12">
-        <f t="shared" si="2"/>
-        <v>2021</v>
-      </c>
-      <c r="S16" s="17">
-        <f t="shared" si="2"/>
-        <v>2021</v>
-      </c>
-      <c r="T16" s="17">
+      <c r="T16" s="12">
         <f t="shared" si="2"/>
         <v>2021</v>
       </c>
@@ -8186,8 +8210,20 @@
         <f t="shared" si="2"/>
         <v>2021</v>
       </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W16" s="17">
+        <f t="shared" si="2"/>
+        <v>2021</v>
+      </c>
+      <c r="X16" s="17">
+        <f t="shared" ref="X16:X32" si="3">X15+K16</f>
+        <v>2021</v>
+      </c>
+      <c r="Y16" s="17">
+        <f t="shared" ref="Y16:Y66" si="4">Y15+L16</f>
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" s="12">
         <v>20</v>
       </c>
@@ -8218,35 +8254,30 @@
       <c r="K17" s="12">
         <v>1</v>
       </c>
-      <c r="M17" s="12">
-        <f t="shared" si="3"/>
+      <c r="L17" s="17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="12">
+        <f t="shared" si="2"/>
         <v>2060</v>
       </c>
-      <c r="N17" s="12">
+      <c r="P17" s="12">
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-      <c r="O17" s="12">
+      <c r="Q17" s="12">
         <f t="shared" si="2"/>
         <v>2037</v>
       </c>
-      <c r="P17" s="12">
+      <c r="R17" s="12">
         <f t="shared" si="2"/>
         <v>2032</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="S17" s="12">
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-      <c r="R17" s="12">
-        <f t="shared" si="2"/>
-        <v>2022</v>
-      </c>
-      <c r="S17" s="17">
-        <f t="shared" si="2"/>
-        <v>2022</v>
-      </c>
-      <c r="T17" s="17">
+      <c r="T17" s="12">
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
@@ -8258,8 +8289,20 @@
         <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W17" s="17">
+        <f t="shared" si="2"/>
+        <v>2022</v>
+      </c>
+      <c r="X17" s="17">
+        <f t="shared" si="3"/>
+        <v>2022</v>
+      </c>
+      <c r="Y17" s="17">
+        <f t="shared" si="4"/>
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>5</v>
       </c>
@@ -8287,44 +8330,51 @@
       <c r="K18" s="12">
         <v>1</v>
       </c>
-      <c r="N18" s="12">
-        <f t="shared" si="2"/>
+      <c r="L18" s="17">
+        <v>1</v>
+      </c>
+      <c r="P18" s="12">
+        <f t="shared" ref="P18:W20" si="5">+P17+C18</f>
         <v>2027</v>
       </c>
-      <c r="O18" s="12">
-        <f t="shared" si="2"/>
+      <c r="Q18" s="12">
+        <f t="shared" si="5"/>
         <v>2042</v>
       </c>
-      <c r="P18" s="12">
-        <f t="shared" si="2"/>
+      <c r="R18" s="12">
+        <f t="shared" si="5"/>
         <v>2037</v>
       </c>
-      <c r="Q18" s="12">
-        <f t="shared" si="2"/>
+      <c r="S18" s="12">
+        <f t="shared" si="5"/>
         <v>2027</v>
       </c>
-      <c r="R18" s="12">
-        <f t="shared" si="2"/>
+      <c r="T18" s="12">
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
-      <c r="S18" s="17">
-        <f t="shared" si="2"/>
+      <c r="U18" s="17">
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
-      <c r="T18" s="17">
-        <f t="shared" si="2"/>
+      <c r="V18" s="17">
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
-      <c r="U18" s="17">
-        <f t="shared" si="2"/>
+      <c r="W18" s="17">
+        <f t="shared" si="5"/>
         <v>2023</v>
       </c>
-      <c r="V18" s="17">
-        <f t="shared" si="2"/>
+      <c r="X18" s="17">
+        <f t="shared" si="3"/>
         <v>2023</v>
       </c>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="Y18" s="17">
+        <f t="shared" si="4"/>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>45</v>
       </c>
@@ -8352,44 +8402,51 @@
       <c r="K19" s="12">
         <v>1</v>
       </c>
-      <c r="N19" s="12">
-        <f t="shared" si="2"/>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12">
+        <f t="shared" si="5"/>
         <v>2072</v>
       </c>
-      <c r="O19" s="12">
-        <f t="shared" si="2"/>
+      <c r="Q19" s="12">
+        <f t="shared" si="5"/>
         <v>2047</v>
       </c>
-      <c r="P19" s="12">
-        <f t="shared" si="2"/>
+      <c r="R19" s="12">
+        <f t="shared" si="5"/>
         <v>2042</v>
       </c>
-      <c r="Q19" s="12">
-        <f t="shared" si="2"/>
+      <c r="S19" s="12">
+        <f t="shared" si="5"/>
         <v>2032</v>
       </c>
-      <c r="R19" s="12">
-        <f t="shared" si="2"/>
+      <c r="T19" s="12">
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
-      <c r="S19" s="17">
-        <f t="shared" si="2"/>
+      <c r="U19" s="17">
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
-      <c r="T19" s="17">
-        <f t="shared" si="2"/>
+      <c r="V19" s="17">
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
-      <c r="U19" s="17">
-        <f t="shared" si="2"/>
+      <c r="W19" s="17">
+        <f t="shared" si="5"/>
         <v>2024</v>
       </c>
-      <c r="V19" s="17">
-        <f t="shared" si="2"/>
+      <c r="X19" s="17">
+        <f t="shared" si="3"/>
         <v>2024</v>
       </c>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="Y19" s="17">
+        <f t="shared" si="4"/>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>25</v>
       </c>
@@ -8417,44 +8474,51 @@
       <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="N20" s="12">
-        <f t="shared" si="2"/>
+      <c r="L20" s="17">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12">
+        <f t="shared" si="5"/>
         <v>2097</v>
       </c>
-      <c r="O20" s="12">
-        <f t="shared" si="2"/>
+      <c r="Q20" s="12">
+        <f t="shared" si="5"/>
         <v>2052</v>
       </c>
-      <c r="P20" s="12">
-        <f t="shared" si="2"/>
+      <c r="R20" s="12">
+        <f t="shared" si="5"/>
         <v>2047</v>
       </c>
-      <c r="Q20" s="12">
-        <f t="shared" si="2"/>
+      <c r="S20" s="12">
+        <f t="shared" si="5"/>
         <v>2037</v>
       </c>
-      <c r="R20" s="12">
-        <f t="shared" si="2"/>
+      <c r="T20" s="12">
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
-      <c r="S20" s="17">
-        <f t="shared" si="2"/>
+      <c r="U20" s="17">
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
-      <c r="T20" s="17">
-        <f t="shared" si="2"/>
+      <c r="V20" s="17">
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
-      <c r="U20" s="17">
-        <f t="shared" si="2"/>
+      <c r="W20" s="17">
+        <f t="shared" si="5"/>
         <v>2025</v>
       </c>
-      <c r="V20" s="17">
-        <f t="shared" si="2"/>
+      <c r="X20" s="17">
+        <f t="shared" si="3"/>
         <v>2025</v>
       </c>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="Y20" s="17">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="C21" s="12">
         <v>5</v>
       </c>
@@ -8480,46 +8544,53 @@
         <v>10</v>
       </c>
       <c r="K21" s="12">
-        <v>3</v>
-      </c>
-      <c r="N21" s="12">
-        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L21" s="17">
+        <v>1</v>
+      </c>
+      <c r="P21" s="12">
+        <f t="shared" ref="P21:V21" si="6">+P20+C21</f>
         <v>2102</v>
       </c>
-      <c r="O21" s="12">
-        <f t="shared" si="2"/>
+      <c r="Q21" s="12">
+        <f t="shared" si="6"/>
         <v>2057</v>
       </c>
-      <c r="P21" s="12">
-        <f t="shared" si="2"/>
+      <c r="R21" s="12">
+        <f t="shared" si="6"/>
         <v>2052</v>
       </c>
-      <c r="Q21" s="12">
-        <f t="shared" si="2"/>
+      <c r="S21" s="12">
+        <f t="shared" si="6"/>
         <v>2042</v>
       </c>
-      <c r="R21" s="12">
-        <f t="shared" si="2"/>
+      <c r="T21" s="12">
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
-      <c r="S21" s="17">
-        <f t="shared" si="2"/>
+      <c r="U21" s="17">
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
-      <c r="T21" s="17">
-        <f t="shared" si="2"/>
+      <c r="V21" s="17">
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
-      <c r="U21" s="17">
-        <f>+U20+J21-5</f>
+      <c r="W21" s="17">
+        <f>+W20+J21-5</f>
         <v>2030</v>
       </c>
-      <c r="V21" s="17">
-        <f>+V20+K21-1</f>
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X21" s="17">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="Y21" s="17">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="D22" s="12">
         <v>5</v>
       </c>
@@ -8542,42 +8613,49 @@
         <v>10</v>
       </c>
       <c r="K22" s="12">
-        <v>4</v>
-      </c>
-      <c r="O22" s="12">
-        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L22" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="12">
+        <f t="shared" ref="Q22:W24" si="7">+Q21+D22</f>
         <v>2062</v>
       </c>
-      <c r="P22" s="12">
-        <f t="shared" si="2"/>
+      <c r="R22" s="12">
+        <f t="shared" si="7"/>
         <v>2057</v>
       </c>
-      <c r="Q22" s="12">
-        <f t="shared" si="2"/>
+      <c r="S22" s="12">
+        <f t="shared" si="7"/>
         <v>2047</v>
       </c>
-      <c r="R22" s="12">
-        <f t="shared" si="2"/>
+      <c r="T22" s="12">
+        <f t="shared" si="7"/>
         <v>2027</v>
       </c>
-      <c r="S22" s="17">
-        <f t="shared" si="2"/>
+      <c r="U22" s="17">
+        <f t="shared" si="7"/>
         <v>2027</v>
       </c>
-      <c r="T22" s="17">
-        <f t="shared" si="2"/>
+      <c r="V22" s="17">
+        <f t="shared" si="7"/>
         <v>2027</v>
       </c>
-      <c r="U22" s="17">
-        <f t="shared" si="2"/>
+      <c r="W22" s="17">
+        <f t="shared" si="7"/>
         <v>2040</v>
       </c>
-      <c r="V22" s="17">
-        <f>+V21+K22-2</f>
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X22" s="17">
+        <f t="shared" si="3"/>
+        <v>2027</v>
+      </c>
+      <c r="Y22" s="17">
+        <f t="shared" si="4"/>
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="D23" s="12">
         <v>5</v>
       </c>
@@ -8602,40 +8680,47 @@
       <c r="K23" s="12">
         <v>5</v>
       </c>
-      <c r="O23" s="12">
-        <f t="shared" si="2"/>
+      <c r="L23" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="12">
+        <f t="shared" si="7"/>
         <v>2067</v>
       </c>
-      <c r="P23" s="12">
-        <f t="shared" si="2"/>
+      <c r="R23" s="12">
+        <f t="shared" si="7"/>
         <v>2062</v>
       </c>
-      <c r="Q23" s="12">
-        <f t="shared" si="2"/>
+      <c r="S23" s="12">
+        <f t="shared" si="7"/>
         <v>2052</v>
       </c>
-      <c r="R23" s="12">
-        <f t="shared" si="2"/>
+      <c r="T23" s="12">
+        <f t="shared" si="7"/>
         <v>2028</v>
       </c>
-      <c r="S23" s="17">
-        <f t="shared" si="2"/>
+      <c r="U23" s="17">
+        <f t="shared" si="7"/>
         <v>2028</v>
       </c>
-      <c r="T23" s="17">
-        <f t="shared" si="2"/>
+      <c r="V23" s="17">
+        <f t="shared" si="7"/>
         <v>2028</v>
       </c>
-      <c r="U23" s="17">
-        <f t="shared" si="2"/>
+      <c r="W23" s="17">
+        <f t="shared" si="7"/>
         <v>2050</v>
       </c>
-      <c r="V23" s="17">
-        <f t="shared" si="2"/>
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X23" s="17">
+        <f t="shared" si="3"/>
+        <v>2032</v>
+      </c>
+      <c r="Y23" s="17">
+        <f t="shared" si="4"/>
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="D24" s="12">
         <v>5</v>
       </c>
@@ -8660,40 +8745,47 @@
       <c r="K24" s="12">
         <v>5</v>
       </c>
-      <c r="O24" s="12">
-        <f t="shared" si="2"/>
+      <c r="L24" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="12">
+        <f t="shared" si="7"/>
         <v>2072</v>
       </c>
-      <c r="P24" s="12">
-        <f t="shared" si="2"/>
+      <c r="R24" s="12">
+        <f t="shared" si="7"/>
         <v>2067</v>
       </c>
-      <c r="Q24" s="12">
-        <f t="shared" si="2"/>
+      <c r="S24" s="12">
+        <f t="shared" si="7"/>
         <v>2057</v>
       </c>
-      <c r="R24" s="12">
-        <f t="shared" si="2"/>
+      <c r="T24" s="12">
+        <f t="shared" si="7"/>
         <v>2029</v>
       </c>
-      <c r="S24" s="17">
-        <f t="shared" si="2"/>
+      <c r="U24" s="17">
+        <f t="shared" si="7"/>
         <v>2029</v>
       </c>
-      <c r="T24" s="17">
-        <f t="shared" si="2"/>
+      <c r="V24" s="17">
+        <f t="shared" si="7"/>
         <v>2029</v>
       </c>
-      <c r="U24" s="17">
-        <f t="shared" si="2"/>
+      <c r="W24" s="17">
+        <f t="shared" si="7"/>
         <v>2060</v>
       </c>
-      <c r="V24" s="17">
-        <f t="shared" si="2"/>
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X24" s="17">
+        <f t="shared" si="3"/>
+        <v>2037</v>
+      </c>
+      <c r="Y24" s="17">
+        <f t="shared" si="4"/>
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E25" s="12">
         <v>5</v>
       </c>
@@ -8715,36 +8807,43 @@
       <c r="K25" s="12">
         <v>5</v>
       </c>
-      <c r="P25" s="12">
-        <f t="shared" si="2"/>
+      <c r="L25" s="17">
+        <v>1</v>
+      </c>
+      <c r="R25" s="12">
+        <f t="shared" ref="R25:W25" si="8">+R24+E25</f>
         <v>2072</v>
       </c>
-      <c r="Q25" s="12">
-        <f t="shared" si="2"/>
+      <c r="S25" s="12">
+        <f t="shared" si="8"/>
         <v>2062</v>
       </c>
-      <c r="R25" s="12">
-        <f t="shared" si="2"/>
+      <c r="T25" s="12">
+        <f t="shared" si="8"/>
         <v>2030</v>
       </c>
-      <c r="S25" s="17">
-        <f t="shared" si="2"/>
+      <c r="U25" s="17">
+        <f t="shared" si="8"/>
         <v>2030</v>
       </c>
-      <c r="T25" s="17">
-        <f t="shared" si="2"/>
+      <c r="V25" s="17">
+        <f t="shared" si="8"/>
         <v>2030</v>
       </c>
-      <c r="U25" s="17">
-        <f t="shared" si="2"/>
+      <c r="W25" s="17">
+        <f t="shared" si="8"/>
         <v>2070</v>
       </c>
-      <c r="V25" s="17">
-        <f t="shared" si="2"/>
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X25" s="17">
+        <f t="shared" si="3"/>
+        <v>2042</v>
+      </c>
+      <c r="Y25" s="17">
+        <f t="shared" si="4"/>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="F26" s="12">
         <v>5</v>
       </c>
@@ -8763,32 +8862,39 @@
       <c r="K26" s="12">
         <v>5</v>
       </c>
-      <c r="Q26" s="12">
-        <f t="shared" si="2"/>
+      <c r="L26" s="17">
+        <v>1</v>
+      </c>
+      <c r="S26" s="12">
+        <f t="shared" ref="S26:W27" si="9">+S25+F26</f>
         <v>2067</v>
       </c>
-      <c r="R26" s="12">
-        <f t="shared" si="2"/>
+      <c r="T26" s="12">
+        <f t="shared" si="9"/>
         <v>2031</v>
       </c>
-      <c r="S26" s="17">
-        <f t="shared" si="2"/>
+      <c r="U26" s="17">
+        <f t="shared" si="9"/>
         <v>2031</v>
       </c>
-      <c r="T26" s="17">
-        <f t="shared" si="2"/>
+      <c r="V26" s="17">
+        <f t="shared" si="9"/>
         <v>2031</v>
       </c>
-      <c r="U26" s="17">
-        <f t="shared" si="2"/>
+      <c r="W26" s="17">
+        <f t="shared" si="9"/>
         <v>2080</v>
       </c>
-      <c r="V26" s="17">
-        <f t="shared" si="2"/>
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X26" s="17">
+        <f t="shared" si="3"/>
+        <v>2047</v>
+      </c>
+      <c r="Y26" s="17">
+        <f t="shared" si="4"/>
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="F27" s="12">
         <v>5</v>
       </c>
@@ -8807,32 +8913,39 @@
       <c r="K27" s="12">
         <v>5</v>
       </c>
-      <c r="Q27" s="12">
-        <f t="shared" si="2"/>
+      <c r="L27" s="17">
+        <v>1</v>
+      </c>
+      <c r="S27" s="12">
+        <f t="shared" si="9"/>
         <v>2072</v>
       </c>
-      <c r="R27" s="12">
-        <f t="shared" si="2"/>
+      <c r="T27" s="12">
+        <f t="shared" si="9"/>
         <v>2032</v>
       </c>
-      <c r="S27" s="17">
-        <f t="shared" si="2"/>
+      <c r="U27" s="17">
+        <f t="shared" si="9"/>
         <v>2032</v>
       </c>
-      <c r="T27" s="17">
-        <f t="shared" si="2"/>
+      <c r="V27" s="17">
+        <f t="shared" si="9"/>
         <v>2032</v>
       </c>
-      <c r="U27" s="17">
-        <f t="shared" si="2"/>
+      <c r="W27" s="17">
+        <f t="shared" si="9"/>
         <v>2090</v>
       </c>
-      <c r="V27" s="17">
-        <f t="shared" si="2"/>
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X27" s="17">
+        <f t="shared" si="3"/>
+        <v>2052</v>
+      </c>
+      <c r="Y27" s="17">
+        <f t="shared" si="4"/>
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G28" s="12">
         <v>5</v>
       </c>
@@ -8848,28 +8961,35 @@
       <c r="K28" s="12">
         <v>5</v>
       </c>
-      <c r="R28" s="12">
-        <f t="shared" si="2"/>
+      <c r="L28" s="17">
+        <v>1</v>
+      </c>
+      <c r="T28" s="12">
+        <f t="shared" ref="T28:W29" si="10">+T27+G28</f>
         <v>2037</v>
       </c>
-      <c r="S28" s="17">
-        <f t="shared" si="2"/>
+      <c r="U28" s="17">
+        <f t="shared" si="10"/>
         <v>2033</v>
       </c>
-      <c r="T28" s="17">
-        <f t="shared" si="2"/>
+      <c r="V28" s="17">
+        <f t="shared" si="10"/>
         <v>2033</v>
       </c>
-      <c r="U28" s="17">
-        <f t="shared" si="2"/>
+      <c r="W28" s="17">
+        <f t="shared" si="10"/>
         <v>2100</v>
       </c>
-      <c r="V28" s="17">
-        <f t="shared" si="2"/>
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X28" s="17">
+        <f t="shared" si="3"/>
+        <v>2057</v>
+      </c>
+      <c r="Y28" s="17">
+        <f t="shared" si="4"/>
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G29" s="12">
         <v>5</v>
       </c>
@@ -8879,27 +8999,41 @@
       <c r="I29" s="17">
         <v>1</v>
       </c>
+      <c r="J29" s="12">
+        <v>10</v>
+      </c>
       <c r="K29" s="12">
         <v>5</v>
       </c>
-      <c r="R29" s="12">
-        <f t="shared" si="2"/>
+      <c r="L29" s="17">
+        <v>1</v>
+      </c>
+      <c r="T29" s="12">
+        <f t="shared" si="10"/>
         <v>2042</v>
       </c>
-      <c r="S29" s="17">
-        <f t="shared" si="2"/>
+      <c r="U29" s="17">
+        <f t="shared" si="10"/>
         <v>2034</v>
       </c>
-      <c r="T29" s="17">
-        <f t="shared" si="2"/>
+      <c r="V29" s="17">
+        <f t="shared" si="10"/>
         <v>2034</v>
       </c>
-      <c r="V29" s="17">
-        <f t="shared" si="2"/>
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W29" s="17">
+        <f t="shared" si="10"/>
+        <v>2110</v>
+      </c>
+      <c r="X29" s="17">
+        <f t="shared" si="3"/>
+        <v>2062</v>
+      </c>
+      <c r="Y29" s="17">
+        <f t="shared" si="4"/>
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G30" s="12">
         <v>5</v>
       </c>
@@ -8912,24 +9046,31 @@
       <c r="K30" s="12">
         <v>5</v>
       </c>
-      <c r="R30" s="12">
-        <f t="shared" ref="R30:T45" si="4">+R29+G30</f>
+      <c r="L30" s="17">
+        <v>1</v>
+      </c>
+      <c r="T30" s="12">
+        <f t="shared" ref="T30:V35" si="11">+T29+G30</f>
         <v>2047</v>
       </c>
-      <c r="S30" s="17">
+      <c r="U30" s="17">
+        <f t="shared" si="11"/>
+        <v>2035</v>
+      </c>
+      <c r="V30" s="17">
+        <f t="shared" si="11"/>
+        <v>2035</v>
+      </c>
+      <c r="X30" s="17">
+        <f t="shared" si="3"/>
+        <v>2067</v>
+      </c>
+      <c r="Y30" s="17">
         <f t="shared" si="4"/>
         <v>2035</v>
       </c>
-      <c r="T30" s="17">
-        <f t="shared" si="4"/>
-        <v>2035</v>
-      </c>
-      <c r="V30" s="17">
-        <f t="shared" ref="V30:V35" si="5">+V29+K30</f>
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="G31" s="12">
         <v>5</v>
       </c>
@@ -8942,362 +9083,616 @@
       <c r="K31" s="12">
         <v>5</v>
       </c>
-      <c r="R31" s="12">
+      <c r="L31" s="17">
+        <v>1</v>
+      </c>
+      <c r="T31" s="12">
+        <f t="shared" si="11"/>
+        <v>2052</v>
+      </c>
+      <c r="U31" s="17">
+        <f t="shared" si="11"/>
+        <v>2036</v>
+      </c>
+      <c r="V31" s="17">
+        <f t="shared" si="11"/>
+        <v>2036</v>
+      </c>
+      <c r="X31" s="17">
+        <f t="shared" si="3"/>
+        <v>2072</v>
+      </c>
+      <c r="Y31" s="17">
+        <f t="shared" si="4"/>
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="G32" s="12">
+        <v>5</v>
+      </c>
+      <c r="H32" s="17">
+        <v>1</v>
+      </c>
+      <c r="I32" s="17">
+        <v>1</v>
+      </c>
+      <c r="K32" s="12">
+        <v>5</v>
+      </c>
+      <c r="L32" s="17">
+        <v>1</v>
+      </c>
+      <c r="T32" s="12">
+        <f t="shared" si="11"/>
+        <v>2057</v>
+      </c>
+      <c r="U32" s="17">
+        <f t="shared" si="11"/>
+        <v>2037</v>
+      </c>
+      <c r="V32" s="17">
+        <f t="shared" si="11"/>
+        <v>2037</v>
+      </c>
+      <c r="X32" s="17">
+        <f t="shared" si="3"/>
+        <v>2077</v>
+      </c>
+      <c r="Y32" s="17">
+        <f t="shared" si="4"/>
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="33" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="G33" s="12">
+        <v>5</v>
+      </c>
+      <c r="H33" s="17">
+        <v>1</v>
+      </c>
+      <c r="I33" s="17">
+        <v>1</v>
+      </c>
+      <c r="L33" s="17">
+        <v>1</v>
+      </c>
+      <c r="T33" s="12">
+        <f t="shared" si="11"/>
+        <v>2062</v>
+      </c>
+      <c r="U33" s="17">
+        <f t="shared" si="11"/>
+        <v>2038</v>
+      </c>
+      <c r="V33" s="17">
+        <f t="shared" si="11"/>
+        <v>2038</v>
+      </c>
+      <c r="Y33" s="17">
+        <f t="shared" si="4"/>
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="34" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="G34" s="12">
+        <v>5</v>
+      </c>
+      <c r="H34" s="17">
+        <v>1</v>
+      </c>
+      <c r="I34" s="17">
+        <v>1</v>
+      </c>
+      <c r="L34" s="17">
+        <v>1</v>
+      </c>
+      <c r="T34" s="12">
+        <f t="shared" si="11"/>
+        <v>2067</v>
+      </c>
+      <c r="U34" s="17">
+        <f t="shared" si="11"/>
+        <v>2039</v>
+      </c>
+      <c r="V34" s="17">
+        <f t="shared" si="11"/>
+        <v>2039</v>
+      </c>
+      <c r="Y34" s="17">
+        <f t="shared" si="4"/>
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="35" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="G35" s="12">
+        <v>5</v>
+      </c>
+      <c r="H35" s="17">
+        <v>1</v>
+      </c>
+      <c r="I35" s="17">
+        <v>1</v>
+      </c>
+      <c r="L35" s="17">
+        <v>1</v>
+      </c>
+      <c r="T35" s="12">
+        <f t="shared" si="11"/>
+        <v>2072</v>
+      </c>
+      <c r="U35" s="17">
+        <f t="shared" si="11"/>
+        <v>2040</v>
+      </c>
+      <c r="V35" s="17">
+        <f t="shared" si="11"/>
+        <v>2040</v>
+      </c>
+      <c r="Y35" s="17">
+        <f t="shared" si="4"/>
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="36" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H36" s="17">
+        <v>1</v>
+      </c>
+      <c r="I36" s="17">
+        <v>1</v>
+      </c>
+      <c r="L36" s="17">
+        <v>1</v>
+      </c>
+      <c r="U36" s="17">
+        <f t="shared" ref="U36:U45" si="12">+U35+H36</f>
+        <v>2041</v>
+      </c>
+      <c r="V36" s="17">
+        <f t="shared" ref="V36:V45" si="13">+V35+I36</f>
+        <v>2041</v>
+      </c>
+      <c r="Y36" s="17">
+        <f t="shared" si="4"/>
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="37" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H37" s="17">
+        <v>1</v>
+      </c>
+      <c r="I37" s="17">
+        <v>1</v>
+      </c>
+      <c r="L37" s="17">
+        <v>1</v>
+      </c>
+      <c r="U37" s="17">
+        <f t="shared" si="12"/>
+        <v>2042</v>
+      </c>
+      <c r="V37" s="17">
+        <f t="shared" si="13"/>
+        <v>2042</v>
+      </c>
+      <c r="Y37" s="17">
+        <f t="shared" si="4"/>
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="38" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H38" s="17">
+        <v>1</v>
+      </c>
+      <c r="I38" s="17">
+        <v>1</v>
+      </c>
+      <c r="L38" s="17">
+        <v>1</v>
+      </c>
+      <c r="U38" s="17">
+        <f t="shared" si="12"/>
+        <v>2043</v>
+      </c>
+      <c r="V38" s="17">
+        <f t="shared" si="13"/>
+        <v>2043</v>
+      </c>
+      <c r="Y38" s="17">
+        <f t="shared" si="4"/>
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="39" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H39" s="17">
+        <v>1</v>
+      </c>
+      <c r="I39" s="17">
+        <v>1</v>
+      </c>
+      <c r="L39" s="17">
+        <v>1</v>
+      </c>
+      <c r="U39" s="17">
+        <f t="shared" si="12"/>
+        <v>2044</v>
+      </c>
+      <c r="V39" s="17">
+        <f t="shared" si="13"/>
+        <v>2044</v>
+      </c>
+      <c r="Y39" s="17">
+        <f t="shared" si="4"/>
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="40" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H40" s="17">
+        <v>1</v>
+      </c>
+      <c r="I40" s="17">
+        <v>1</v>
+      </c>
+      <c r="L40" s="17">
+        <v>1</v>
+      </c>
+      <c r="U40" s="17">
+        <f t="shared" si="12"/>
+        <v>2045</v>
+      </c>
+      <c r="V40" s="17">
+        <f t="shared" si="13"/>
+        <v>2045</v>
+      </c>
+      <c r="Y40" s="17">
+        <f t="shared" si="4"/>
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="41" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H41" s="17">
+        <v>1</v>
+      </c>
+      <c r="I41" s="17">
+        <v>1</v>
+      </c>
+      <c r="L41" s="17">
+        <v>1</v>
+      </c>
+      <c r="U41" s="17">
+        <f t="shared" si="12"/>
+        <v>2046</v>
+      </c>
+      <c r="V41" s="17">
+        <f t="shared" si="13"/>
+        <v>2046</v>
+      </c>
+      <c r="Y41" s="17">
+        <f t="shared" si="4"/>
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="42" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H42" s="17">
+        <v>1</v>
+      </c>
+      <c r="I42" s="17">
+        <v>1</v>
+      </c>
+      <c r="L42" s="17">
+        <v>1</v>
+      </c>
+      <c r="U42" s="17">
+        <f t="shared" si="12"/>
+        <v>2047</v>
+      </c>
+      <c r="V42" s="17">
+        <f t="shared" si="13"/>
+        <v>2047</v>
+      </c>
+      <c r="Y42" s="17">
+        <f t="shared" si="4"/>
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="43" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H43" s="17">
+        <v>1</v>
+      </c>
+      <c r="I43" s="17">
+        <v>1</v>
+      </c>
+      <c r="L43" s="17">
+        <v>1</v>
+      </c>
+      <c r="U43" s="17">
+        <f t="shared" si="12"/>
+        <v>2048</v>
+      </c>
+      <c r="V43" s="17">
+        <f t="shared" si="13"/>
+        <v>2048</v>
+      </c>
+      <c r="Y43" s="17">
+        <f t="shared" si="4"/>
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="44" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H44" s="17">
+        <v>1</v>
+      </c>
+      <c r="I44" s="17">
+        <v>1</v>
+      </c>
+      <c r="L44" s="17">
+        <v>1</v>
+      </c>
+      <c r="U44" s="17">
+        <f t="shared" si="12"/>
+        <v>2049</v>
+      </c>
+      <c r="V44" s="17">
+        <f t="shared" si="13"/>
+        <v>2049</v>
+      </c>
+      <c r="Y44" s="17">
+        <f t="shared" si="4"/>
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="45" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="H45" s="17">
+        <v>1</v>
+      </c>
+      <c r="I45" s="17">
+        <v>1</v>
+      </c>
+      <c r="L45" s="17">
+        <v>1</v>
+      </c>
+      <c r="U45" s="17">
+        <f t="shared" si="12"/>
+        <v>2050</v>
+      </c>
+      <c r="V45" s="17">
+        <f t="shared" si="13"/>
+        <v>2050</v>
+      </c>
+      <c r="Y45" s="17">
+        <f t="shared" si="4"/>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="46" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="I46" s="17">
+        <v>1</v>
+      </c>
+      <c r="L46" s="17">
+        <v>1</v>
+      </c>
+      <c r="V46" s="17">
+        <f>+V45+I46</f>
+        <v>2051</v>
+      </c>
+      <c r="Y46" s="17">
+        <f t="shared" si="4"/>
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="47" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="I47" s="17">
+        <v>1</v>
+      </c>
+      <c r="L47" s="17">
+        <v>1</v>
+      </c>
+      <c r="V47" s="17">
+        <f>+V46+I47</f>
+        <v>2052</v>
+      </c>
+      <c r="Y47" s="17">
         <f t="shared" si="4"/>
         <v>2052</v>
       </c>
-      <c r="S31" s="17">
+    </row>
+    <row r="48" spans="7:25" x14ac:dyDescent="0.25">
+      <c r="I48" s="17">
+        <v>5</v>
+      </c>
+      <c r="L48" s="17">
+        <v>1</v>
+      </c>
+      <c r="V48" s="17">
+        <f>+V47+I48-2</f>
+        <v>2055</v>
+      </c>
+      <c r="Y48" s="17">
         <f t="shared" si="4"/>
-        <v>2036</v>
-      </c>
-      <c r="T31" s="17">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="49" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="I49" s="17">
+        <v>5</v>
+      </c>
+      <c r="L49" s="17">
+        <v>1</v>
+      </c>
+      <c r="V49" s="17">
+        <f>+V48+I49</f>
+        <v>2060</v>
+      </c>
+      <c r="Y49" s="17">
         <f t="shared" si="4"/>
-        <v>2036</v>
-      </c>
-      <c r="V31" s="17">
-        <f t="shared" si="5"/>
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G32" s="12">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="50" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="I50" s="17">
         <v>5</v>
       </c>
-      <c r="H32" s="17">
-        <v>1</v>
-      </c>
-      <c r="I32" s="17">
-        <v>1</v>
-      </c>
-      <c r="K32" s="12">
+      <c r="L50" s="17">
+        <v>1</v>
+      </c>
+      <c r="V50" s="17">
+        <f>+V49+I50</f>
+        <v>2065</v>
+      </c>
+      <c r="Y50" s="17">
+        <f t="shared" si="4"/>
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="51" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="I51" s="17">
         <v>5</v>
       </c>
-      <c r="R32" s="12">
+      <c r="L51" s="17">
+        <v>1</v>
+      </c>
+      <c r="V51" s="17">
+        <f>+V50+I51</f>
+        <v>2070</v>
+      </c>
+      <c r="Y51" s="17">
+        <f t="shared" si="4"/>
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="52" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L52" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="17">
         <f t="shared" si="4"/>
         <v>2057</v>
       </c>
-      <c r="S32" s="17">
+    </row>
+    <row r="53" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L53" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="17">
         <f t="shared" si="4"/>
-        <v>2037</v>
-      </c>
-      <c r="T32" s="17">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="54" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L54" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="17">
         <f t="shared" si="4"/>
-        <v>2037</v>
-      </c>
-      <c r="V32" s="17">
-        <f t="shared" si="5"/>
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="33" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="G33" s="12">
-        <v>5</v>
-      </c>
-      <c r="H33" s="17">
-        <v>1</v>
-      </c>
-      <c r="I33" s="17">
-        <v>1</v>
-      </c>
-      <c r="K33" s="12">
-        <v>5</v>
-      </c>
-      <c r="R33" s="12">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="55" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L55" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="17">
+        <f t="shared" si="4"/>
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="56" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L56" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="17">
+        <f t="shared" si="4"/>
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="57" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L57" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="17">
         <f t="shared" si="4"/>
         <v>2062</v>
       </c>
-      <c r="S33" s="17">
+    </row>
+    <row r="58" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L58" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="17">
         <f t="shared" si="4"/>
-        <v>2038</v>
-      </c>
-      <c r="T33" s="17">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="59" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L59" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="17">
         <f t="shared" si="4"/>
-        <v>2038</v>
-      </c>
-      <c r="V33" s="17">
-        <f t="shared" si="5"/>
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="34" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="G34" s="12">
-        <v>5</v>
-      </c>
-      <c r="H34" s="17">
-        <v>1</v>
-      </c>
-      <c r="I34" s="17">
-        <v>1</v>
-      </c>
-      <c r="K34" s="12">
-        <v>5</v>
-      </c>
-      <c r="R34" s="12">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="60" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L60" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="17">
+        <f t="shared" si="4"/>
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="61" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L61" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="17">
+        <f t="shared" si="4"/>
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="62" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L62" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y62" s="17">
         <f t="shared" si="4"/>
         <v>2067</v>
       </c>
-      <c r="S34" s="17">
+    </row>
+    <row r="63" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L63" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="17">
         <f t="shared" si="4"/>
-        <v>2039</v>
-      </c>
-      <c r="T34" s="17">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="64" spans="9:25" x14ac:dyDescent="0.25">
+      <c r="L64" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="17">
         <f t="shared" si="4"/>
-        <v>2039</v>
-      </c>
-      <c r="V34" s="17">
-        <f t="shared" si="5"/>
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="35" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="G35" s="12">
-        <v>5</v>
-      </c>
-      <c r="H35" s="17">
-        <v>1</v>
-      </c>
-      <c r="I35" s="17">
-        <v>1</v>
-      </c>
-      <c r="K35" s="12">
-        <v>5</v>
-      </c>
-      <c r="R35" s="12">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="65" spans="12:25" x14ac:dyDescent="0.25">
+      <c r="L65" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="17">
         <f t="shared" si="4"/>
-        <v>2072</v>
-      </c>
-      <c r="S35" s="17">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="66" spans="12:25" x14ac:dyDescent="0.25">
+      <c r="L66" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="17">
         <f t="shared" si="4"/>
-        <v>2040</v>
-      </c>
-      <c r="T35" s="17">
-        <f t="shared" si="4"/>
-        <v>2040</v>
-      </c>
-      <c r="V35" s="17">
-        <f t="shared" si="5"/>
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="36" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H36" s="17">
-        <v>1</v>
-      </c>
-      <c r="I36" s="17">
-        <v>1</v>
-      </c>
-      <c r="K36" s="12">
-        <v>5</v>
-      </c>
-      <c r="S36" s="17">
-        <f t="shared" si="4"/>
-        <v>2041</v>
-      </c>
-      <c r="T36" s="17">
-        <f t="shared" si="4"/>
-        <v>2041</v>
-      </c>
-      <c r="V36" s="17">
-        <f>+V35+K36</f>
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="37" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H37" s="17">
-        <v>1</v>
-      </c>
-      <c r="I37" s="17">
-        <v>1</v>
-      </c>
-      <c r="S37" s="17">
-        <f t="shared" si="4"/>
-        <v>2042</v>
-      </c>
-      <c r="T37" s="17">
-        <f t="shared" si="4"/>
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="38" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H38" s="17">
-        <v>1</v>
-      </c>
-      <c r="I38" s="17">
-        <v>1</v>
-      </c>
-      <c r="S38" s="17">
-        <f t="shared" si="4"/>
-        <v>2043</v>
-      </c>
-      <c r="T38" s="17">
-        <f t="shared" si="4"/>
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="39" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H39" s="17">
-        <v>1</v>
-      </c>
-      <c r="I39" s="17">
-        <v>1</v>
-      </c>
-      <c r="S39" s="17">
-        <f t="shared" si="4"/>
-        <v>2044</v>
-      </c>
-      <c r="T39" s="17">
-        <f t="shared" si="4"/>
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="40" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H40" s="17">
-        <v>1</v>
-      </c>
-      <c r="I40" s="17">
-        <v>1</v>
-      </c>
-      <c r="S40" s="17">
-        <f t="shared" si="4"/>
-        <v>2045</v>
-      </c>
-      <c r="T40" s="17">
-        <f t="shared" si="4"/>
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="41" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H41" s="17">
-        <v>1</v>
-      </c>
-      <c r="I41" s="17">
-        <v>1</v>
-      </c>
-      <c r="S41" s="17">
-        <f t="shared" si="4"/>
-        <v>2046</v>
-      </c>
-      <c r="T41" s="17">
-        <f t="shared" si="4"/>
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="42" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H42" s="17">
-        <v>1</v>
-      </c>
-      <c r="I42" s="17">
-        <v>1</v>
-      </c>
-      <c r="S42" s="17">
-        <f t="shared" si="4"/>
-        <v>2047</v>
-      </c>
-      <c r="T42" s="17">
-        <f t="shared" si="4"/>
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="43" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H43" s="17">
-        <v>1</v>
-      </c>
-      <c r="I43" s="17">
-        <v>1</v>
-      </c>
-      <c r="S43" s="17">
-        <f t="shared" si="4"/>
-        <v>2048</v>
-      </c>
-      <c r="T43" s="17">
-        <f t="shared" si="4"/>
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="44" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H44" s="17">
-        <v>1</v>
-      </c>
-      <c r="I44" s="17">
-        <v>1</v>
-      </c>
-      <c r="S44" s="17">
-        <f t="shared" si="4"/>
-        <v>2049</v>
-      </c>
-      <c r="T44" s="17">
-        <f t="shared" si="4"/>
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="45" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="H45" s="17">
-        <v>1</v>
-      </c>
-      <c r="I45" s="17">
-        <v>1</v>
-      </c>
-      <c r="S45" s="17">
-        <f t="shared" si="4"/>
-        <v>2050</v>
-      </c>
-      <c r="T45" s="17">
-        <f t="shared" si="4"/>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="46" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="I46" s="17">
-        <v>1</v>
-      </c>
-      <c r="T46" s="17">
-        <f>+T45+I46</f>
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="47" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="I47" s="17">
-        <v>1</v>
-      </c>
-      <c r="T47" s="17">
-        <f>+T46+I47</f>
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="48" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="I48" s="17">
-        <v>5</v>
-      </c>
-      <c r="T48" s="17">
-        <f>+T47+I48-2</f>
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="49" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I49" s="17">
-        <v>5</v>
-      </c>
-      <c r="T49" s="17">
-        <f t="shared" ref="T49:T51" si="6">+T48+I49</f>
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="50" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I50" s="17">
-        <v>5</v>
-      </c>
-      <c r="T50" s="17">
-        <f t="shared" si="6"/>
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="51" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I51" s="17">
-        <v>5</v>
-      </c>
-      <c r="T51" s="17">
-        <f t="shared" si="6"/>
-        <v>2070</v>
+        <v>2071</v>
       </c>
     </row>
   </sheetData>
@@ -9314,7 +9709,7 @@
   <dimension ref="B3:C9"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.6640625" customWidth="1"/>
+    <col min="2" max="2" width="52.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -9383,11 +9778,11 @@
   <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
     <col min="7" max="7" width="6.44140625" customWidth="1"/>
-    <col min="8" max="8" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9842,10 +10237,10 @@
   <dimension ref="B1:G34"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" customWidth="1"/>
     <col min="6" max="6" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="10.44140625" customWidth="1"/>
   </cols>
@@ -10651,7 +11046,7 @@
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="4" width="13.88671875" customWidth="1"/>
+    <col min="3" max="4" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
